--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98667</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96013</v>
+        <v>96015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96156</v>
+        <v>96158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98667</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97541</v>
+        <v>97543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98667</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96015</v>
+        <v>96022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97543</v>
+        <v>97550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96022</v>
+        <v>96024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97550</v>
+        <v>97552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96024</v>
+        <v>96050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97552</v>
+        <v>97578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96050</v>
+        <v>96051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96051</v>
+        <v>96052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97579</v>
+        <v>97580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96052</v>
+        <v>96056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97580</v>
+        <v>97584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96056</v>
+        <v>96058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97584</v>
+        <v>97586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96058</v>
+        <v>96062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97586</v>
+        <v>97590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96062</v>
+        <v>96070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97590</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96070</v>
+        <v>96073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96073</v>
+        <v>96102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97601</v>
+        <v>97630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129242542</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129242536</v>
       </c>
       <c r="B3" t="n">
-        <v>96102</v>
+        <v>96114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129242507</v>
       </c>
       <c r="B4" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129242031</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>129242527</v>
       </c>
       <c r="B7" t="n">
-        <v>97630</v>
+        <v>97642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>129242095</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,6 +1558,131 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129874795</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Barrskog vid Svinsätter, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>576354</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6469879</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Valdemarsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ringarum</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>E-Val-0333</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Sammanställt från 3 rapporter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46766-2025 artfynd.xlsx
+++ b/artfynd/A 46766-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
         <v>129874795</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
